--- a/outputs/Cowpeas_percentile_classification_matrix.xlsx
+++ b/outputs/Cowpeas_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="91">
   <si>
     <t>2020 Mar</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>Yambio</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>Minimal</t>
@@ -841,67 +844,67 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s">
         <v>77</v>
       </c>
       <c r="H2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T2" t="s">
         <v>77</v>
       </c>
       <c r="U2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z2" t="s">
         <v>77</v>
@@ -979,13 +982,13 @@
         <v>77</v>
       </c>
       <c r="AY2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AZ2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BA2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:53">
@@ -1044,7 +1047,7 @@
         <v>77</v>
       </c>
       <c r="S3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T3" t="s">
         <v>77</v>
@@ -1140,13 +1143,13 @@
         <v>77</v>
       </c>
       <c r="AY3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AZ3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BA3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:53">
@@ -1154,55 +1157,55 @@
         <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
         <v>77</v>
       </c>
       <c r="F4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s">
         <v>77</v>
       </c>
       <c r="H4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K4" t="s">
         <v>77</v>
       </c>
       <c r="L4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q4" t="s">
         <v>77</v>
       </c>
       <c r="R4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S4" t="s">
         <v>77</v>
@@ -1214,64 +1217,64 @@
         <v>77</v>
       </c>
       <c r="V4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE4" t="s">
         <v>77</v>
       </c>
       <c r="AF4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ4" t="s">
         <v>77</v>
       </c>
       <c r="AK4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM4" t="s">
         <v>77</v>
       </c>
       <c r="AN4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AP4" t="s">
         <v>77</v>
@@ -1280,34 +1283,34 @@
         <v>77</v>
       </c>
       <c r="AR4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AS4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AT4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU4" t="s">
         <v>77</v>
       </c>
       <c r="AV4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW4" t="s">
         <v>77</v>
       </c>
       <c r="AX4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:53">
@@ -1366,67 +1369,67 @@
         <v>77</v>
       </c>
       <c r="S5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T5" t="s">
         <v>77</v>
       </c>
       <c r="U5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X5" t="s">
         <v>77</v>
       </c>
       <c r="Y5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z5" t="s">
         <v>77</v>
       </c>
       <c r="AA5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG5" t="s">
         <v>77</v>
       </c>
       <c r="AH5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI5" t="s">
         <v>77</v>
       </c>
       <c r="AJ5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AN5" t="s">
         <v>77</v>
@@ -1438,37 +1441,37 @@
         <v>77</v>
       </c>
       <c r="AQ5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AX5" t="s">
         <v>79</v>
       </c>
-      <c r="AR5" t="s">
-        <v>77</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>77</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>77</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>77</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>77</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>79</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>78</v>
-      </c>
       <c r="AY5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="BA5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:53">
@@ -1581,19 +1584,19 @@
         <v>77</v>
       </c>
       <c r="AK6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL6" t="s">
         <v>77</v>
       </c>
       <c r="AM6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AN6" t="s">
         <v>77</v>
       </c>
       <c r="AO6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AP6" t="s">
         <v>77</v>
@@ -1602,19 +1605,19 @@
         <v>77</v>
       </c>
       <c r="AR6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AS6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AT6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AU6" t="s">
         <v>77</v>
       </c>
       <c r="AV6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AW6" t="s">
         <v>77</v>
@@ -1623,13 +1626,13 @@
         <v>77</v>
       </c>
       <c r="AY6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AZ6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BA6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:53">
@@ -1691,22 +1694,22 @@
         <v>77</v>
       </c>
       <c r="T7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U7" t="s">
         <v>77</v>
       </c>
       <c r="V7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z7" t="s">
         <v>77</v>
@@ -1715,37 +1718,37 @@
         <v>77</v>
       </c>
       <c r="AB7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI7" t="s">
         <v>77</v>
       </c>
       <c r="AJ7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM7" t="s">
         <v>77</v>
@@ -1757,13 +1760,13 @@
         <v>77</v>
       </c>
       <c r="AP7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ7" t="s">
         <v>77</v>
       </c>
       <c r="AR7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS7" t="s">
         <v>77</v>
@@ -1784,13 +1787,13 @@
         <v>77</v>
       </c>
       <c r="AY7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AZ7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:53">
@@ -1810,13 +1813,13 @@
         <v>77</v>
       </c>
       <c r="F8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s">
         <v>77</v>
       </c>
       <c r="H8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I8" t="s">
         <v>77</v>
@@ -1831,31 +1834,31 @@
         <v>77</v>
       </c>
       <c r="M8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O8" t="s">
         <v>77</v>
       </c>
       <c r="P8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R8" t="s">
         <v>77</v>
       </c>
       <c r="S8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T8" t="s">
         <v>77</v>
       </c>
       <c r="U8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V8" t="s">
         <v>77</v>
@@ -1864,31 +1867,31 @@
         <v>77</v>
       </c>
       <c r="X8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE8" t="s">
         <v>77</v>
       </c>
       <c r="AF8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG8" t="s">
         <v>77</v>
@@ -1909,19 +1912,19 @@
         <v>77</v>
       </c>
       <c r="AM8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AN8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AO8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AP8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AQ8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AR8" t="s">
         <v>77</v>
@@ -1945,13 +1948,13 @@
         <v>77</v>
       </c>
       <c r="AY8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AZ8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BA8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:53">
@@ -1968,7 +1971,7 @@
         <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F9" t="s">
         <v>77</v>
@@ -1977,7 +1980,7 @@
         <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I9" t="s">
         <v>77</v>
@@ -2010,7 +2013,7 @@
         <v>77</v>
       </c>
       <c r="S9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T9" t="s">
         <v>77</v>
@@ -2019,52 +2022,52 @@
         <v>77</v>
       </c>
       <c r="V9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W9" t="s">
         <v>77</v>
       </c>
       <c r="X9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y9" t="s">
         <v>77</v>
       </c>
       <c r="Z9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA9" t="s">
         <v>77</v>
       </c>
       <c r="AB9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC9" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF9" t="s">
         <v>79</v>
       </c>
-      <c r="AD9" t="s">
-        <v>77</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>77</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>78</v>
-      </c>
       <c r="AG9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL9" t="s">
         <v>77</v>
@@ -2091,28 +2094,28 @@
         <v>77</v>
       </c>
       <c r="AT9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AV9" t="s">
         <v>77</v>
       </c>
       <c r="AW9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AX9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AY9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AZ9" t="s">
         <v>83</v>
       </c>
-      <c r="AZ9" t="s">
-        <v>82</v>
-      </c>
       <c r="BA9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:53">
@@ -2234,46 +2237,46 @@
         <v>77</v>
       </c>
       <c r="AN10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AO10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AP10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AQ10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AR10" t="s">
         <v>77</v>
       </c>
       <c r="AS10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AT10" t="s">
         <v>77</v>
       </c>
       <c r="AU10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AV10" t="s">
         <v>77</v>
       </c>
       <c r="AW10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AX10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AY10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AZ10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BA10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:53">
@@ -2389,10 +2392,10 @@
         <v>77</v>
       </c>
       <c r="AL11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AN11" t="s">
         <v>77</v>
@@ -2422,19 +2425,19 @@
         <v>77</v>
       </c>
       <c r="AW11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AX11" t="s">
         <v>77</v>
       </c>
       <c r="AY11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AZ11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BA11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:53">
@@ -2547,7 +2550,7 @@
         <v>77</v>
       </c>
       <c r="AK12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL12" t="s">
         <v>77</v>
@@ -2556,7 +2559,7 @@
         <v>77</v>
       </c>
       <c r="AN12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AO12" t="s">
         <v>77</v>
@@ -2565,7 +2568,7 @@
         <v>77</v>
       </c>
       <c r="AQ12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AR12" t="s">
         <v>77</v>
@@ -2577,7 +2580,7 @@
         <v>77</v>
       </c>
       <c r="AU12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AV12" t="s">
         <v>77</v>
@@ -2589,13 +2592,13 @@
         <v>77</v>
       </c>
       <c r="AY12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AZ12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BA12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:53">
@@ -2606,25 +2609,25 @@
         <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
         <v>77</v>
       </c>
       <c r="E13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s">
         <v>77</v>
       </c>
       <c r="I13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J13" t="s">
         <v>77</v>
@@ -2636,19 +2639,19 @@
         <v>77</v>
       </c>
       <c r="M13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O13" t="s">
         <v>77</v>
       </c>
       <c r="P13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R13" t="s">
         <v>77</v>
@@ -2675,88 +2678,88 @@
         <v>77</v>
       </c>
       <c r="Z13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AP13" t="s">
+        <v>80</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AX13" t="s">
         <v>79</v>
       </c>
-      <c r="AQ13" t="s">
-        <v>77</v>
-      </c>
-      <c r="AR13" t="s">
-        <v>77</v>
-      </c>
-      <c r="AS13" t="s">
-        <v>77</v>
-      </c>
-      <c r="AT13" t="s">
-        <v>77</v>
-      </c>
-      <c r="AU13" t="s">
-        <v>77</v>
-      </c>
-      <c r="AV13" t="s">
-        <v>77</v>
-      </c>
-      <c r="AW13" t="s">
-        <v>77</v>
-      </c>
-      <c r="AX13" t="s">
-        <v>78</v>
-      </c>
       <c r="AY13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AZ13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="BA13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:53">
@@ -2767,28 +2770,28 @@
         <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F14" t="s">
         <v>77</v>
       </c>
       <c r="G14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K14" t="s">
         <v>77</v>
@@ -2800,16 +2803,16 @@
         <v>77</v>
       </c>
       <c r="N14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R14" t="s">
         <v>77</v>
@@ -2818,16 +2821,16 @@
         <v>77</v>
       </c>
       <c r="T14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X14" t="s">
         <v>77</v>
@@ -2836,28 +2839,28 @@
         <v>77</v>
       </c>
       <c r="Z14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA14" t="s">
         <v>77</v>
       </c>
       <c r="AB14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE14" t="s">
         <v>77</v>
       </c>
       <c r="AF14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH14" t="s">
         <v>77</v>
@@ -2866,58 +2869,58 @@
         <v>77</v>
       </c>
       <c r="AJ14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AN14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AO14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AP14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AQ14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AR14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AS14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AT14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU14" t="s">
         <v>77</v>
       </c>
       <c r="AV14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AW14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AX14" t="s">
         <v>77</v>
       </c>
       <c r="AY14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AZ14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="BA14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:53">
@@ -2928,34 +2931,34 @@
         <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
         <v>77</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I15" t="s">
         <v>77</v>
       </c>
       <c r="J15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M15" t="s">
         <v>77</v>
@@ -2964,28 +2967,28 @@
         <v>77</v>
       </c>
       <c r="O15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U15" t="s">
         <v>77</v>
       </c>
       <c r="V15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W15" t="s">
         <v>77</v>
@@ -2994,7 +2997,7 @@
         <v>77</v>
       </c>
       <c r="Y15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z15" t="s">
         <v>77</v>
@@ -3009,52 +3012,52 @@
         <v>77</v>
       </c>
       <c r="AD15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH15" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>80</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR15" t="s">
         <v>79</v>
       </c>
-      <c r="AI15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AM15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AO15" t="s">
-        <v>79</v>
-      </c>
-      <c r="AP15" t="s">
-        <v>79</v>
-      </c>
-      <c r="AQ15" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR15" t="s">
-        <v>78</v>
-      </c>
       <c r="AS15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AT15" t="s">
         <v>77</v>
@@ -3063,22 +3066,22 @@
         <v>77</v>
       </c>
       <c r="AV15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW15" t="s">
         <v>77</v>
       </c>
       <c r="AX15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AY15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AZ15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:53">
@@ -3110,10 +3113,10 @@
         <v>77</v>
       </c>
       <c r="J16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L16" t="s">
         <v>77</v>
@@ -3122,25 +3125,25 @@
         <v>77</v>
       </c>
       <c r="N16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P16" t="s">
         <v>77</v>
       </c>
       <c r="Q16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U16" t="s">
         <v>77</v>
@@ -3149,49 +3152,49 @@
         <v>77</v>
       </c>
       <c r="W16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z16" t="s">
         <v>77</v>
       </c>
       <c r="AA16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD16" t="s">
         <v>77</v>
       </c>
       <c r="AE16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG16" t="s">
         <v>77</v>
       </c>
       <c r="AH16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI16" t="s">
         <v>77</v>
       </c>
       <c r="AJ16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL16" t="s">
         <v>77</v>
@@ -3203,10 +3206,10 @@
         <v>77</v>
       </c>
       <c r="AO16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AP16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AQ16" t="s">
         <v>77</v>
@@ -3221,25 +3224,25 @@
         <v>77</v>
       </c>
       <c r="AU16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AV16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AW16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AX16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AY16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AZ16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="BA16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:53">
@@ -3298,16 +3301,16 @@
         <v>77</v>
       </c>
       <c r="S17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W17" t="s">
         <v>77</v>
@@ -3394,13 +3397,13 @@
         <v>77</v>
       </c>
       <c r="AY17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AZ17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BA17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:53">
@@ -3408,34 +3411,34 @@
         <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E18" t="s">
         <v>77</v>
       </c>
       <c r="F18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I18" t="s">
         <v>77</v>
       </c>
       <c r="J18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L18" t="s">
         <v>77</v>
@@ -3447,10 +3450,10 @@
         <v>77</v>
       </c>
       <c r="O18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q18" t="s">
         <v>77</v>
@@ -3459,73 +3462,73 @@
         <v>77</v>
       </c>
       <c r="S18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V18" t="s">
         <v>77</v>
       </c>
       <c r="W18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z18" t="s">
         <v>77</v>
       </c>
       <c r="AA18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC18" t="s">
         <v>77</v>
       </c>
       <c r="AD18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF18" t="s">
         <v>77</v>
       </c>
       <c r="AG18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK18" t="s">
         <v>77</v>
       </c>
       <c r="AL18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AP18" t="s">
         <v>77</v>
@@ -3534,13 +3537,13 @@
         <v>77</v>
       </c>
       <c r="AR18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AT18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AU18" t="s">
         <v>77</v>
@@ -3552,16 +3555,16 @@
         <v>77</v>
       </c>
       <c r="AX18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AZ18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="BA18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:53">
@@ -3569,25 +3572,25 @@
         <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
         <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F19" t="s">
         <v>77</v>
       </c>
       <c r="G19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I19" t="s">
         <v>77</v>
@@ -3641,13 +3644,13 @@
         <v>77</v>
       </c>
       <c r="Z19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC19" t="s">
         <v>77</v>
@@ -3659,13 +3662,13 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI19" t="s">
         <v>77</v>
@@ -3677,19 +3680,19 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM19" t="s">
         <v>77</v>
       </c>
       <c r="AN19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AO19" t="s">
         <v>77</v>
       </c>
       <c r="AP19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AQ19" t="s">
         <v>77</v>
@@ -3698,7 +3701,7 @@
         <v>77</v>
       </c>
       <c r="AS19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AT19" t="s">
         <v>77</v>
@@ -3707,22 +3710,22 @@
         <v>77</v>
       </c>
       <c r="AV19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AW19" t="s">
         <v>77</v>
       </c>
       <c r="AX19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AZ19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BA19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:53">
@@ -3733,7 +3736,7 @@
         <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s">
         <v>77</v>
@@ -3742,148 +3745,148 @@
         <v>77</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L20" t="s">
         <v>77</v>
       </c>
       <c r="M20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U20" t="s">
         <v>77</v>
       </c>
       <c r="V20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W20" t="s">
         <v>77</v>
       </c>
       <c r="X20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB20" t="s">
         <v>77</v>
       </c>
       <c r="AC20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD20" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM20" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN20" t="s">
         <v>79</v>
       </c>
-      <c r="AE20" t="s">
-        <v>77</v>
-      </c>
-      <c r="AF20" t="s">
+      <c r="AO20" t="s">
+        <v>77</v>
+      </c>
+      <c r="AP20" t="s">
+        <v>77</v>
+      </c>
+      <c r="AQ20" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR20" t="s">
+        <v>77</v>
+      </c>
+      <c r="AS20" t="s">
+        <v>78</v>
+      </c>
+      <c r="AT20" t="s">
+        <v>77</v>
+      </c>
+      <c r="AU20" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV20" t="s">
         <v>79</v>
       </c>
-      <c r="AG20" t="s">
+      <c r="AW20" t="s">
         <v>79</v>
       </c>
-      <c r="AH20" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI20" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ20" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK20" t="s">
-        <v>77</v>
-      </c>
-      <c r="AL20" t="s">
-        <v>77</v>
-      </c>
-      <c r="AM20" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN20" t="s">
-        <v>78</v>
-      </c>
-      <c r="AO20" t="s">
-        <v>77</v>
-      </c>
-      <c r="AP20" t="s">
-        <v>77</v>
-      </c>
-      <c r="AQ20" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR20" t="s">
-        <v>77</v>
-      </c>
-      <c r="AS20" t="s">
-        <v>77</v>
-      </c>
-      <c r="AT20" t="s">
-        <v>77</v>
-      </c>
-      <c r="AU20" t="s">
-        <v>77</v>
-      </c>
-      <c r="AV20" t="s">
-        <v>78</v>
-      </c>
-      <c r="AW20" t="s">
-        <v>78</v>
-      </c>
       <c r="AX20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AZ20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="BA20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:53">
@@ -3912,25 +3915,25 @@
         <v>77</v>
       </c>
       <c r="I21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K21" t="s">
         <v>77</v>
       </c>
       <c r="L21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P21" t="s">
         <v>77</v>
@@ -3948,16 +3951,16 @@
         <v>77</v>
       </c>
       <c r="U21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y21" t="s">
         <v>77</v>
@@ -3966,52 +3969,52 @@
         <v>77</v>
       </c>
       <c r="AA21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE21" t="s">
         <v>77</v>
       </c>
       <c r="AF21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG21" t="s">
         <v>77</v>
       </c>
       <c r="AH21" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL21" t="s">
         <v>79</v>
       </c>
-      <c r="AI21" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK21" t="s">
-        <v>77</v>
-      </c>
-      <c r="AL21" t="s">
-        <v>78</v>
-      </c>
       <c r="AM21" t="s">
         <v>77</v>
       </c>
       <c r="AN21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO21" t="s">
         <v>77</v>
       </c>
       <c r="AP21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AQ21" t="s">
         <v>77</v>
@@ -4020,7 +4023,7 @@
         <v>77</v>
       </c>
       <c r="AS21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AT21" t="s">
         <v>77</v>
@@ -4029,22 +4032,22 @@
         <v>77</v>
       </c>
       <c r="AV21" t="s">
+        <v>80</v>
+      </c>
+      <c r="AW21" t="s">
         <v>79</v>
       </c>
-      <c r="AW21" t="s">
-        <v>78</v>
-      </c>
       <c r="AX21" t="s">
         <v>77</v>
       </c>
       <c r="AY21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="BA21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:53">
@@ -4052,16 +4055,16 @@
         <v>73</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
         <v>77</v>
       </c>
       <c r="E22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F22" t="s">
         <v>77</v>
@@ -4070,40 +4073,40 @@
         <v>77</v>
       </c>
       <c r="H22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K22" t="s">
         <v>77</v>
       </c>
       <c r="L22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M22" t="s">
         <v>77</v>
       </c>
       <c r="N22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q22" t="s">
         <v>77</v>
       </c>
       <c r="R22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T22" t="s">
         <v>77</v>
@@ -4112,37 +4115,37 @@
         <v>77</v>
       </c>
       <c r="V22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W22" t="s">
         <v>77</v>
       </c>
       <c r="X22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y22" t="s">
         <v>77</v>
       </c>
       <c r="Z22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA22" t="s">
         <v>77</v>
       </c>
       <c r="AB22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC22" t="s">
         <v>77</v>
       </c>
       <c r="AD22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG22" t="s">
         <v>77</v>
@@ -4151,34 +4154,34 @@
         <v>77</v>
       </c>
       <c r="AI22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ22" t="s">
         <v>77</v>
       </c>
       <c r="AK22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL22" t="s">
         <v>77</v>
       </c>
       <c r="AM22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN22" t="s">
         <v>77</v>
       </c>
       <c r="AO22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AP22" t="s">
         <v>77</v>
       </c>
       <c r="AQ22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS22" t="s">
         <v>77</v>
@@ -4190,7 +4193,7 @@
         <v>77</v>
       </c>
       <c r="AV22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW22" t="s">
         <v>77</v>
@@ -4199,13 +4202,13 @@
         <v>77</v>
       </c>
       <c r="AY22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AZ22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="BA22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:53">
@@ -4321,7 +4324,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM23" t="s">
         <v>77</v>
@@ -4333,7 +4336,7 @@
         <v>77</v>
       </c>
       <c r="AP23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AQ23" t="s">
         <v>77</v>
@@ -4360,13 +4363,13 @@
         <v>77</v>
       </c>
       <c r="AY23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AZ23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BA23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:53">
@@ -4383,31 +4386,31 @@
         <v>77</v>
       </c>
       <c r="E24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s">
         <v>77</v>
       </c>
       <c r="H24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J24" t="s">
         <v>77</v>
       </c>
       <c r="K24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N24" t="s">
         <v>77</v>
@@ -4416,10 +4419,10 @@
         <v>77</v>
       </c>
       <c r="P24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R24" t="s">
         <v>77</v>
@@ -4431,10 +4434,10 @@
         <v>77</v>
       </c>
       <c r="U24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W24" t="s">
         <v>77</v>
@@ -4443,34 +4446,34 @@
         <v>77</v>
       </c>
       <c r="Y24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z24" t="s">
         <v>77</v>
       </c>
       <c r="AA24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF24" t="s">
         <v>77</v>
       </c>
       <c r="AG24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI24" t="s">
         <v>77</v>
@@ -4479,34 +4482,34 @@
         <v>77</v>
       </c>
       <c r="AK24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL24" t="s">
         <v>77</v>
       </c>
       <c r="AM24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AN24" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO24" t="s">
+        <v>77</v>
+      </c>
+      <c r="AP24" t="s">
+        <v>80</v>
+      </c>
+      <c r="AQ24" t="s">
+        <v>77</v>
+      </c>
+      <c r="AR24" t="s">
         <v>79</v>
       </c>
-      <c r="AO24" t="s">
-        <v>77</v>
-      </c>
-      <c r="AP24" t="s">
-        <v>79</v>
-      </c>
-      <c r="AQ24" t="s">
-        <v>77</v>
-      </c>
-      <c r="AR24" t="s">
-        <v>78</v>
-      </c>
       <c r="AS24" t="s">
         <v>77</v>
       </c>
       <c r="AT24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU24" t="s">
         <v>77</v>
@@ -4515,19 +4518,19 @@
         <v>77</v>
       </c>
       <c r="AW24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AY24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="BA24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:53">
@@ -4538,34 +4541,34 @@
         <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F25" t="s">
         <v>77</v>
       </c>
       <c r="G25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K25" t="s">
         <v>77</v>
       </c>
       <c r="L25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M25" t="s">
         <v>77</v>
@@ -4574,121 +4577,121 @@
         <v>77</v>
       </c>
       <c r="O25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W25" t="s">
         <v>77</v>
       </c>
       <c r="X25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD25" t="s">
         <v>77</v>
       </c>
       <c r="AE25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI25" t="s">
         <v>77</v>
       </c>
       <c r="AJ25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL25" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM25" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO25" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP25" t="s">
+        <v>77</v>
+      </c>
+      <c r="AQ25" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR25" t="s">
+        <v>77</v>
+      </c>
+      <c r="AS25" t="s">
         <v>79</v>
       </c>
-      <c r="AM25" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN25" t="s">
-        <v>79</v>
-      </c>
-      <c r="AO25" t="s">
-        <v>79</v>
-      </c>
-      <c r="AP25" t="s">
-        <v>77</v>
-      </c>
-      <c r="AQ25" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR25" t="s">
-        <v>77</v>
-      </c>
-      <c r="AS25" t="s">
-        <v>78</v>
-      </c>
       <c r="AT25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AU25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AV25" t="s">
         <v>77</v>
       </c>
       <c r="AW25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AY25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AZ25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="BA25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Cowpeas_percentile_classification_matrix.xlsx
+++ b/outputs/Cowpeas_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="80">
   <si>
     <t>2020 Mar</t>
   </si>
@@ -253,40 +253,7 @@
     <t>Minimal</t>
   </si>
   <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Alarm</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>8%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>2%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>12%</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>16%</t>
   </si>
 </sst>
 </file>
@@ -853,7 +820,7 @@
         <v>77</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I2" t="s">
         <v>78</v>
@@ -871,13 +838,13 @@
         <v>78</v>
       </c>
       <c r="N2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q2" t="s">
         <v>78</v>
@@ -886,7 +853,7 @@
         <v>78</v>
       </c>
       <c r="S2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T2" t="s">
         <v>77</v>
@@ -982,13 +949,13 @@
         <v>77</v>
       </c>
       <c r="AY2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AZ2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="BA2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:53">
@@ -1047,7 +1014,7 @@
         <v>77</v>
       </c>
       <c r="S3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T3" t="s">
         <v>77</v>
@@ -1143,13 +1110,13 @@
         <v>77</v>
       </c>
       <c r="AY3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AZ3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="BA3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:53">
@@ -1262,16 +1229,16 @@
         <v>77</v>
       </c>
       <c r="AK4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AL4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AM4" t="s">
         <v>77</v>
       </c>
       <c r="AN4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AO4" t="s">
         <v>78</v>
@@ -1289,28 +1256,28 @@
         <v>78</v>
       </c>
       <c r="AT4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AU4" t="s">
         <v>77</v>
       </c>
       <c r="AV4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AW4" t="s">
         <v>77</v>
       </c>
       <c r="AX4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AY4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AZ4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="BA4" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:53">
@@ -1375,7 +1342,7 @@
         <v>77</v>
       </c>
       <c r="U5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="V5" t="s">
         <v>78</v>
@@ -1396,13 +1363,13 @@
         <v>78</v>
       </c>
       <c r="AB5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AC5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AD5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AE5" t="s">
         <v>78</v>
@@ -1441,7 +1408,7 @@
         <v>77</v>
       </c>
       <c r="AQ5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AR5" t="s">
         <v>78</v>
@@ -1459,19 +1426,19 @@
         <v>78</v>
       </c>
       <c r="AW5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AX5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AY5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AZ5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="BA5" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:53">
@@ -1584,19 +1551,19 @@
         <v>77</v>
       </c>
       <c r="AK6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL6" t="s">
         <v>77</v>
       </c>
       <c r="AM6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AN6" t="s">
         <v>77</v>
       </c>
       <c r="AO6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AP6" t="s">
         <v>77</v>
@@ -1605,19 +1572,19 @@
         <v>77</v>
       </c>
       <c r="AR6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AS6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AT6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AU6" t="s">
         <v>77</v>
       </c>
       <c r="AV6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AW6" t="s">
         <v>77</v>
@@ -1626,13 +1593,13 @@
         <v>77</v>
       </c>
       <c r="AY6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AZ6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="BA6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:53">
@@ -1703,7 +1670,7 @@
         <v>78</v>
       </c>
       <c r="W7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="X7" t="s">
         <v>78</v>
@@ -1718,37 +1685,37 @@
         <v>77</v>
       </c>
       <c r="AB7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AC7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AD7" t="s">
         <v>78</v>
       </c>
       <c r="AE7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AF7" t="s">
         <v>78</v>
       </c>
       <c r="AG7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AI7" t="s">
         <v>77</v>
       </c>
       <c r="AJ7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AK7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AL7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AM7" t="s">
         <v>77</v>
@@ -1760,13 +1727,13 @@
         <v>77</v>
       </c>
       <c r="AP7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AQ7" t="s">
         <v>77</v>
       </c>
       <c r="AR7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AS7" t="s">
         <v>77</v>
@@ -1787,13 +1754,13 @@
         <v>77</v>
       </c>
       <c r="AY7" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AZ7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="BA7" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:53">
@@ -1858,7 +1825,7 @@
         <v>77</v>
       </c>
       <c r="U8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="V8" t="s">
         <v>77</v>
@@ -1867,7 +1834,7 @@
         <v>77</v>
       </c>
       <c r="X8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Y8" t="s">
         <v>78</v>
@@ -1885,7 +1852,7 @@
         <v>78</v>
       </c>
       <c r="AD8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AE8" t="s">
         <v>77</v>
@@ -1948,13 +1915,13 @@
         <v>77</v>
       </c>
       <c r="AY8" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AZ8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="BA8" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:53">
@@ -2013,7 +1980,7 @@
         <v>77</v>
       </c>
       <c r="S9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T9" t="s">
         <v>77</v>
@@ -2040,22 +2007,22 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AC9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AD9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AE9" t="s">
         <v>77</v>
       </c>
       <c r="AF9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AG9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s">
         <v>78</v>
@@ -2094,7 +2061,7 @@
         <v>77</v>
       </c>
       <c r="AT9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AU9" t="s">
         <v>78</v>
@@ -2109,13 +2076,13 @@
         <v>78</v>
       </c>
       <c r="AY9" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AZ9" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="BA9" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:53">
@@ -2237,46 +2204,46 @@
         <v>77</v>
       </c>
       <c r="AN10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AO10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AP10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AQ10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AR10" t="s">
         <v>77</v>
       </c>
       <c r="AS10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AT10" t="s">
         <v>77</v>
       </c>
       <c r="AU10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AV10" t="s">
         <v>77</v>
       </c>
       <c r="AW10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AX10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AY10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AZ10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="BA10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:53">
@@ -2392,10 +2359,10 @@
         <v>77</v>
       </c>
       <c r="AL11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AM11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AN11" t="s">
         <v>77</v>
@@ -2425,19 +2392,19 @@
         <v>77</v>
       </c>
       <c r="AW11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AX11" t="s">
         <v>77</v>
       </c>
       <c r="AY11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AZ11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="BA11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:53">
@@ -2550,7 +2517,7 @@
         <v>77</v>
       </c>
       <c r="AK12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL12" t="s">
         <v>77</v>
@@ -2559,7 +2526,7 @@
         <v>77</v>
       </c>
       <c r="AN12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AO12" t="s">
         <v>77</v>
@@ -2568,7 +2535,7 @@
         <v>77</v>
       </c>
       <c r="AQ12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AR12" t="s">
         <v>77</v>
@@ -2580,7 +2547,7 @@
         <v>77</v>
       </c>
       <c r="AU12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AV12" t="s">
         <v>77</v>
@@ -2592,13 +2559,13 @@
         <v>77</v>
       </c>
       <c r="AY12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AZ12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="BA12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:53">
@@ -2705,7 +2672,7 @@
         <v>78</v>
       </c>
       <c r="AI13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AJ13" t="s">
         <v>78</v>
@@ -2717,16 +2684,16 @@
         <v>78</v>
       </c>
       <c r="AM13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AN13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AO13" t="s">
         <v>78</v>
       </c>
       <c r="AP13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AQ13" t="s">
         <v>78</v>
@@ -2750,16 +2717,16 @@
         <v>78</v>
       </c>
       <c r="AX13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AY13" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AZ13" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="BA13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:53">
@@ -2830,7 +2797,7 @@
         <v>78</v>
       </c>
       <c r="W14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="X14" t="s">
         <v>77</v>
@@ -2890,16 +2857,16 @@
         <v>78</v>
       </c>
       <c r="AQ14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AR14" t="s">
         <v>78</v>
       </c>
       <c r="AS14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AT14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AU14" t="s">
         <v>77</v>
@@ -2914,13 +2881,13 @@
         <v>77</v>
       </c>
       <c r="AY14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AZ14" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="BA14" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:53">
@@ -2967,7 +2934,7 @@
         <v>77</v>
       </c>
       <c r="O15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P15" t="s">
         <v>78</v>
@@ -3024,7 +2991,7 @@
         <v>78</v>
       </c>
       <c r="AH15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="s">
         <v>78</v>
@@ -3045,16 +3012,16 @@
         <v>78</v>
       </c>
       <c r="AO15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AP15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AQ15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AR15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AS15" t="s">
         <v>78</v>
@@ -3066,22 +3033,22 @@
         <v>77</v>
       </c>
       <c r="AV15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AW15" t="s">
         <v>77</v>
       </c>
       <c r="AX15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AY15" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AZ15" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="BA15" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:53">
@@ -3128,7 +3095,7 @@
         <v>78</v>
       </c>
       <c r="O16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P16" t="s">
         <v>77</v>
@@ -3164,10 +3131,10 @@
         <v>77</v>
       </c>
       <c r="AA16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AB16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AC16" t="s">
         <v>78</v>
@@ -3224,7 +3191,7 @@
         <v>77</v>
       </c>
       <c r="AU16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AV16" t="s">
         <v>78</v>
@@ -3236,13 +3203,13 @@
         <v>78</v>
       </c>
       <c r="AY16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AZ16" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="BA16" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:53">
@@ -3301,16 +3268,16 @@
         <v>77</v>
       </c>
       <c r="S17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="U17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="V17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="W17" t="s">
         <v>77</v>
@@ -3397,13 +3364,13 @@
         <v>77</v>
       </c>
       <c r="AY17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AZ17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="BA17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:53">
@@ -3480,7 +3447,7 @@
         <v>78</v>
       </c>
       <c r="Y18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Z18" t="s">
         <v>77</v>
@@ -3495,10 +3462,10 @@
         <v>77</v>
       </c>
       <c r="AD18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AE18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AF18" t="s">
         <v>77</v>
@@ -3510,7 +3477,7 @@
         <v>78</v>
       </c>
       <c r="AI18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AJ18" t="s">
         <v>78</v>
@@ -3522,13 +3489,13 @@
         <v>78</v>
       </c>
       <c r="AM18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AN18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AO18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AP18" t="s">
         <v>77</v>
@@ -3537,7 +3504,7 @@
         <v>77</v>
       </c>
       <c r="AR18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AS18" t="s">
         <v>78</v>
@@ -3555,16 +3522,16 @@
         <v>77</v>
       </c>
       <c r="AX18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AY18" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AZ18" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="BA18" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:53">
@@ -3581,13 +3548,13 @@
         <v>78</v>
       </c>
       <c r="E19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F19" t="s">
         <v>77</v>
       </c>
       <c r="G19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s">
         <v>78</v>
@@ -3647,7 +3614,7 @@
         <v>78</v>
       </c>
       <c r="AA19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AB19" t="s">
         <v>78</v>
@@ -3668,7 +3635,7 @@
         <v>78</v>
       </c>
       <c r="AH19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AI19" t="s">
         <v>77</v>
@@ -3692,7 +3659,7 @@
         <v>77</v>
       </c>
       <c r="AP19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AQ19" t="s">
         <v>77</v>
@@ -3710,22 +3677,22 @@
         <v>77</v>
       </c>
       <c r="AV19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AW19" t="s">
         <v>77</v>
       </c>
       <c r="AX19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AY19" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AZ19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="BA19" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:53">
@@ -3817,19 +3784,19 @@
         <v>78</v>
       </c>
       <c r="AD20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AE20" t="s">
         <v>78</v>
       </c>
       <c r="AF20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AG20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AH20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI20" t="s">
         <v>78</v>
@@ -3844,10 +3811,10 @@
         <v>78</v>
       </c>
       <c r="AM20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AN20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AO20" t="s">
         <v>77</v>
@@ -3856,7 +3823,7 @@
         <v>77</v>
       </c>
       <c r="AQ20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AR20" t="s">
         <v>77</v>
@@ -3871,22 +3838,22 @@
         <v>78</v>
       </c>
       <c r="AV20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AX20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AY20" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AZ20" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="BA20" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:53">
@@ -3975,7 +3942,7 @@
         <v>78</v>
       </c>
       <c r="AC21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AD21" t="s">
         <v>78</v>
@@ -3984,13 +3951,13 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AG21" t="s">
         <v>77</v>
       </c>
       <c r="AH21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI21" t="s">
         <v>78</v>
@@ -4002,13 +3969,13 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AM21" t="s">
         <v>77</v>
       </c>
       <c r="AN21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AO21" t="s">
         <v>77</v>
@@ -4032,22 +3999,22 @@
         <v>77</v>
       </c>
       <c r="AV21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AW21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AX21" t="s">
         <v>77</v>
       </c>
       <c r="AY21" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AZ21" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="BA21" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:53">
@@ -4076,7 +4043,7 @@
         <v>78</v>
       </c>
       <c r="I22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J22" t="s">
         <v>78</v>
@@ -4154,19 +4121,19 @@
         <v>77</v>
       </c>
       <c r="AI22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AJ22" t="s">
         <v>77</v>
       </c>
       <c r="AK22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL22" t="s">
         <v>77</v>
       </c>
       <c r="AM22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AN22" t="s">
         <v>77</v>
@@ -4178,10 +4145,10 @@
         <v>77</v>
       </c>
       <c r="AQ22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AR22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AS22" t="s">
         <v>77</v>
@@ -4193,7 +4160,7 @@
         <v>77</v>
       </c>
       <c r="AV22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AW22" t="s">
         <v>77</v>
@@ -4202,13 +4169,13 @@
         <v>77</v>
       </c>
       <c r="AY22" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AZ22" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="BA22" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:53">
@@ -4324,7 +4291,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AM23" t="s">
         <v>77</v>
@@ -4336,7 +4303,7 @@
         <v>77</v>
       </c>
       <c r="AP23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AQ23" t="s">
         <v>77</v>
@@ -4363,13 +4330,13 @@
         <v>77</v>
       </c>
       <c r="AY23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AZ23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="BA23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:53">
@@ -4404,10 +4371,10 @@
         <v>77</v>
       </c>
       <c r="K24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M24" t="s">
         <v>78</v>
@@ -4464,7 +4431,7 @@
         <v>78</v>
       </c>
       <c r="AE24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AF24" t="s">
         <v>77</v>
@@ -4491,25 +4458,25 @@
         <v>78</v>
       </c>
       <c r="AN24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AO24" t="s">
         <v>77</v>
       </c>
       <c r="AP24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AQ24" t="s">
         <v>77</v>
       </c>
       <c r="AR24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AS24" t="s">
         <v>77</v>
       </c>
       <c r="AT24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AU24" t="s">
         <v>77</v>
@@ -4518,19 +4485,19 @@
         <v>77</v>
       </c>
       <c r="AW24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AX24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AY24" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AZ24" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="BA24" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:53">
@@ -4586,7 +4553,7 @@
         <v>78</v>
       </c>
       <c r="R25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S25" t="s">
         <v>78</v>
@@ -4628,7 +4595,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AG25" t="s">
         <v>78</v>
@@ -4640,58 +4607,58 @@
         <v>77</v>
       </c>
       <c r="AJ25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AK25" t="s">
         <v>78</v>
       </c>
       <c r="AL25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AM25" t="s">
         <v>77</v>
       </c>
       <c r="AN25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AO25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AP25" t="s">
         <v>77</v>
       </c>
       <c r="AQ25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AR25" t="s">
         <v>77</v>
       </c>
       <c r="AS25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AT25" t="s">
         <v>78</v>
       </c>
       <c r="AU25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AV25" t="s">
         <v>77</v>
       </c>
       <c r="AW25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AX25" t="s">
         <v>78</v>
       </c>
       <c r="AY25" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AZ25" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="BA25" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Cowpeas_percentile_classification_matrix.xlsx
+++ b/outputs/Cowpeas_percentile_classification_matrix.xlsx
@@ -250,7 +250,7 @@
     <t>No data</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>0%</t>
